--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486798_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486798_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2696</v>
+        <v>2.4672</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7852</v>
+        <v>2.7097</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.2425</v>
       </c>
       <c r="G2" t="n">
         <v>0.8781</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.809</v>
+        <v>1.0066</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6543</v>
+        <v>0.5788</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1547</v>
+        <v>0.4278</v>
       </c>
       <c r="V2" t="n">
         <v>2.1271</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.989</v>
+        <v>1.5101</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8276</v>
+        <v>2.8205</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8386</v>
+        <v>-1.3104</v>
       </c>
       <c r="G3" t="n">
         <v>0.5476</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2038</v>
+        <v>0.3173</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4347</v>
+        <v>-0.4418</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2309</v>
+        <v>0.7591</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8995</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2842</v>
+        <v>0.7408</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.304</v>
+        <v>-0.1454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.8862</v>
       </c>
       <c r="G4" t="n">
         <v>0.5091</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0978</v>
+        <v>-0.6412</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>-0.3657</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5735</v>
+        <v>-0.2756</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2856</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5915</v>
+        <v>-1.2728</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0101</v>
+        <v>-1.3177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4186</v>
+        <v>0.0449</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4753</v>
+        <v>-0.8839</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0819</v>
+        <v>-0.5244</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3934</v>
+        <v>-0.3595</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7366</v>
+        <v>-1.1727</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7366</v>
+        <v>-0.5239</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6488</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7387</v>
+        <v>0.2889</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3453</v>
+        <v>-0.0005</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3934</v>
+        <v>0.2893</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>2.019</v>
+        <v>-0.6826</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4063</v>
+        <v>-0.145</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6127</v>
+        <v>-0.5376</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3282</v>
+        <v>-0.2856</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8205</v>
+        <v>-1.4706</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6418</v>
+        <v>-0.1186</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1786</v>
+        <v>-1.352</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8839</v>
+        <v>-1.5325</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5244</v>
+        <v>-1.0758</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3595</v>
+        <v>-0.4567</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1727</v>
+        <v>-0.2356</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5239</v>
+        <v>-0.317</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6488</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2889</v>
+        <v>-1.2969</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0005</v>
+        <v>-0.7588</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2893</v>
+        <v>-0.5381</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2302</v>
+        <v>0.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4691</v>
+        <v>0.1171</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7611</v>
+        <v>-0.0551</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8305</v>
+        <v>-1.8243</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4288</v>
+        <v>-2.0443</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4017</v>
+        <v>0.22</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5325</v>
+        <v>-2.4753</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0758</v>
+        <v>-2.0819</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4567</v>
+        <v>-0.3934</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2356</v>
+        <v>-1.7366</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.317</v>
+        <v>-1.7366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2969</v>
+        <v>-0.7387</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7588</v>
+        <v>-0.3453</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5381</v>
+        <v>-0.3934</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.298</v>
+        <v>0.7861</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1932</v>
+        <v>0.372</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1048</v>
+        <v>0.414</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5077</v>
+        <v>-2.2778</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0275</v>
+        <v>-2.3261</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4802</v>
+        <v>0.0483</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.476</v>
+        <v>-1.7534</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2553</v>
+        <v>1.2962</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2208</v>
+        <v>-3.0496</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0207</v>
+        <v>-0.4832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>1.5039</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.9871</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4967</v>
+        <v>-1.2703</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2759</v>
+        <v>-0.2077</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2208</v>
+        <v>-1.0626</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0663</v>
+        <v>0.1241</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0828</v>
+        <v>-0.2211</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0166</v>
+        <v>0.3452</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6959</v>
+        <v>-2.3794</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4208</v>
+        <v>-0.9241</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2751</v>
+        <v>-1.4553</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5804</v>
+        <v>-1.476</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4203</v>
+        <v>-0.2553</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0007</v>
+        <v>-1.2208</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1934</v>
+        <v>0.0207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1448</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3383</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3869</v>
+        <v>-1.4967</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2755</v>
+        <v>-0.2759</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6624</v>
+        <v>-1.2208</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8992</v>
+        <v>0.062</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5243</v>
+        <v>0.0206</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3749</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2783</v>
+        <v>-2.431</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2249</v>
+        <v>-2.2553</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5033</v>
+        <v>-0.1758</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0382</v>
+        <v>-1.5804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5389</v>
+        <v>0.4203</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5771</v>
+        <v>-2.0007</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2113</v>
+        <v>-1.1934</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3672</v>
+        <v>0.1448</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1559</v>
+        <v>-1.3383</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2495</v>
+        <v>-0.3869</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8283</v>
+        <v>0.2755</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4212</v>
+        <v>-0.6624</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9545</v>
+        <v>-0.6343</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2487</v>
+        <v>-0.3587</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7058</v>
+        <v>-0.2756</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>0.9421</v>
       </c>
       <c r="W10" t="n">
         <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5133</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4942</v>
+        <v>-2.9997</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.319</v>
+        <v>1.2801</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1752</v>
+        <v>-4.2798</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7534</v>
+        <v>-2.0382</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2962</v>
+        <v>0.5389</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0496</v>
+        <v>-2.5771</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4832</v>
+        <v>1.2113</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5039</v>
+        <v>1.3672</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9871</v>
+        <v>-0.1559</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2703</v>
+        <v>-3.2495</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2077</v>
+        <v>-0.8283</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0626</v>
+        <v>-2.4212</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0923</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.214</v>
+        <v>-0.1936</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1217</v>
+        <v>-0.4823</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5712</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5191</v>
+        <v>-3.1592</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1244</v>
+        <v>-1.8141</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3947</v>
+        <v>-1.3451</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4142</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1049</v>
+        <v>0.255</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.138</v>
+        <v>0.1723</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.242</v>
+        <v>-5.2365</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6083</v>
+        <v>-2.8082</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6337</v>
+        <v>-2.4283</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7112</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7396</v>
+        <v>-0.255</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.028</v>
+        <v>-0.2279</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7675999999999999</v>
+        <v>-0.0271</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8842</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.4369</v>
+        <v>-18.3332</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.046999999999999</v>
+        <v>-6.943499999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.3899</v>
+        <v>-11.3898</v>
       </c>
       <c r="G14" t="n">
         <v>-15.9303</v>
       </c>
       <c r="H14" t="n">
-        <v>2.415</v>
+        <v>2.414999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-18.3454</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.437300000000001</v>
+        <v>-0.4373000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>6.559</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.996299999999999</v>
+        <v>-6.996300000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-15.4928</v>
@@ -1537,7 +1537,7 @@
         <v>-11.3492</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.99999999995449e-05</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-9.654000000000002</v>
@@ -1546,13 +1546,13 @@
         <v>9.6538</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.379400000000001</v>
+        <v>-0.2759999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7965</v>
+        <v>-0.6930000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4172000000000003</v>
+        <v>0.4170000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1272</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.1104</v>
+        <v>7.5933</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9113</v>
+        <v>6.3942</v>
       </c>
       <c r="F15" t="n">
         <v>1.1991</v>
@@ -1624,10 +1624,10 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7723</v>
+        <v>0.2552</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.0893</v>
       </c>
       <c r="U15" t="n">
         <v>0.1659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.8238</v>
+        <v>6.7355</v>
       </c>
       <c r="E16" t="n">
-        <v>6.6609</v>
+        <v>6.1438</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1629</v>
+        <v>0.5918</v>
       </c>
       <c r="G16" t="n">
         <v>4.4459</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6056</v>
+        <v>0.5173</v>
       </c>
       <c r="T16" t="n">
-        <v>0.165</v>
+        <v>-0.3522</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4406</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.6138</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0819</v>
+        <v>3.8903</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3184</v>
+        <v>1.8013</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7635</v>
+        <v>2.089</v>
       </c>
       <c r="G17" t="n">
         <v>2.3664</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1363</v>
+        <v>0.9446</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9099</v>
+        <v>0.3927</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2264</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARTINEZ SERNA</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0975</v>
+        <v>2.4044</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8359</v>
+        <v>0.9987</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2616</v>
+        <v>1.4057</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2423</v>
+        <v>2.2731</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.3786</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1529</v>
+        <v>1.8944</v>
       </c>
       <c r="J18" t="n">
-        <v>1.167</v>
+        <v>2.5366</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4345</v>
+        <v>1.0694</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7325</v>
+        <v>1.4672</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.2635</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3451</v>
+        <v>-0.6907</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4205</v>
+        <v>0.4272</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1874</v>
+        <v>-0.1309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.138</v>
+        <v>-0.6417</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0494</v>
+        <v>0.5108</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>D. MARTINEZ SERNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0115</v>
+        <v>2.3677</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4816</v>
+        <v>1.0427</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5299</v>
+        <v>1.325</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2731</v>
+        <v>1.2423</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3786</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8944</v>
+        <v>1.1529</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5366</v>
+        <v>1.167</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0694</v>
+        <v>0.4345</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4672</v>
+        <v>0.7325</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2635</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6907</v>
+        <v>-0.3451</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4272</v>
+        <v>0.4205</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5239</v>
+        <v>0.0828</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1588</v>
+        <v>0.0688</v>
       </c>
       <c r="U19" t="n">
-        <v>0.635</v>
+        <v>0.014</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8727</v>
+        <v>1.918</v>
       </c>
       <c r="E20" t="n">
-        <v>1.616</v>
+        <v>2.2365</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7433</v>
+        <v>-0.3185</v>
       </c>
       <c r="G20" t="n">
         <v>3.4325</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8108</v>
+        <v>0.2346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7725</v>
+        <v>-0.152</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0382</v>
+        <v>0.3866</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5559</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2499</v>
+        <v>1.1389</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1783</v>
+        <v>0.1396</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4282</v>
+        <v>0.9993</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1918</v>
+        <v>0.3322</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6552</v>
+        <v>-0.6828</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4634</v>
+        <v>1.015</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0213</v>
+        <v>0.1191</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2763</v>
+        <v>0.0761</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2976</v>
+        <v>0.043</v>
       </c>
       <c r="M21" t="n">
         <v>0.2131</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6211</v>
+        <v>-0.759</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8341</v>
+        <v>0.972</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4523</v>
+        <v>0.2275</v>
       </c>
       <c r="T21" t="n">
-        <v>0.11</v>
+        <v>0.2135</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3423</v>
+        <v>0.014</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1225</v>
+        <v>0.4664</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3775</v>
+        <v>-1.0749</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5001</v>
+        <v>1.5413</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3322</v>
+        <v>0.1918</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6828</v>
+        <v>0.6552</v>
       </c>
       <c r="I22" t="n">
-        <v>1.015</v>
+        <v>-0.4634</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1191</v>
+        <v>-0.0213</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0761</v>
+        <v>1.2763</v>
       </c>
       <c r="L22" t="n">
-        <v>0.043</v>
+        <v>-1.2976</v>
       </c>
       <c r="M22" t="n">
         <v>0.2131</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.759</v>
+        <v>-0.6211</v>
       </c>
       <c r="O22" t="n">
-        <v>0.972</v>
+        <v>0.8341</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7889</v>
+        <v>0.6688</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3036</v>
+        <v>0.2134</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4853</v>
+        <v>0.4554</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2249</v>
+        <v>-0.1229</v>
       </c>
       <c r="E23" t="n">
         <v>-1.085</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8602</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4153</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5187</v>
+        <v>0.6206</v>
       </c>
       <c r="T23" t="n">
         <v>0.4411</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0776</v>
+        <v>0.1795</v>
       </c>
       <c r="V23" t="n">
         <v>0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8018</v>
+        <v>-0.7025</v>
       </c>
       <c r="E24" t="n">
         <v>-0.4276</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3742</v>
+        <v>-0.2749</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1658</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4855</v>
+        <v>-0.3862</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2096</v>
+        <v>-0.1102</v>
       </c>
       <c r="V24" t="n">
         <v>0.0426</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.031</v>
+        <v>-2.2252</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.78</v>
+        <v>-2.2971</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.251</v>
+        <v>0.0718</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7191</v>
@@ -2404,13 +2404,13 @@
         <v>1.1585</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0608</v>
+        <v>-0.2551</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3857</v>
+        <v>-0.1314</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4465</v>
+        <v>-0.1237</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2856</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.8758</v>
+        <v>-2.6482</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5857</v>
+        <v>-2.4823</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.29</v>
+        <v>-0.1659</v>
       </c>
       <c r="G26" t="n">
         <v>-2.6274</v>
@@ -2482,13 +2482,13 @@
         <v>0.1931</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2483</v>
+        <v>-0.0207</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3863</v>
+        <v>-0.2829</v>
       </c>
       <c r="U26" t="n">
-        <v>0.138</v>
+        <v>0.2621</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.4367</v>
+        <v>20.8157</v>
       </c>
       <c r="E27" t="n">
-        <v>11.39</v>
+        <v>11.3899</v>
       </c>
       <c r="F27" t="n">
-        <v>8.047000000000002</v>
+        <v>9.425899999999999</v>
       </c>
       <c r="G27" t="n">
         <v>15.9304</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4151</v>
+        <v>-2.415100000000001</v>
       </c>
       <c r="I27" t="n">
         <v>18.34519999999999</v>
@@ -2545,7 +2545,7 @@
         <v>0.4371999999999998</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.558999999999999</v>
+        <v>-6.559</v>
       </c>
       <c r="O27" t="n">
         <v>6.9961</v>
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-9.654200000000001</v>
+        <v>-9.654199999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>9.6539</v>
+        <v>9.653899999999998</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3796</v>
+        <v>2.7585</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4170000000000001</v>
+        <v>-0.4173</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7968</v>
+        <v>3.175800000000001</v>
       </c>
       <c r="V27" t="n">
         <v>2.1271</v>
